--- a/1_Data/Feldborg_2021_IJERPH/CodeBook_Feldborg_2021_IJERPH_Exp1_Clean.xlsx
+++ b/1_Data/Feldborg_2021_IJERPH/CodeBook_Feldborg_2021_IJERPH_Exp1_Clean.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,26 +413,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Variable_name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Variable_description</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Variable_value</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Variable_category</t>
         </is>
@@ -480,29 +468,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Inquisit raw group code (1/2); has no correspondence to any paper factor. Participants are NOT split into groups (Dataset_inf subj_Group = All, 2026-09 decision: GAD-7 questionnaire scores only, no clinical diagnosis).</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>1;2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Numerical</t>
+          <t>Categorical</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Block number in the experiment; each block may contain practice or experimental trials</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -519,12 +507,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Trial</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Block number in the experiment; each block may contain practice or experimental trials</t>
+          <t>Trial number within the block</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -541,39 +529,39 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Trial</t>
+          <t>Shape</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Trial number within the block</t>
+          <t>Visual shape stimulus presented in the trial</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>ve.tif;he.tif</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Numerical</t>
+          <t>Categorical</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Shape</t>
+          <t>Label</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Visual shape stimulus presented in the trial</t>
+          <t>Text label presented for matching with the shape</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ve.tif;he.tif</t>
+          <t>self;friend;stranger</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -585,17 +573,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Text label presented for matching with the shape</t>
+          <t>Task type: the kind of shape-label matching task performed in the trial (default self-matching; other tasks e.g. facialExpression-matching, monetaryValue-matching, self-pseudoWords)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>self;friend;stranger</t>
+          <t>self-matching</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -761,17 +749,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Response</t>
+          <t>extraIV1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Participant's response in the trial</t>
+          <t>Emotion condition of the shape stimulus (line = control: three vertical lines): happy/line/neutral/sad</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>48;47;0</t>
+          <t>happy;line;neutral;sad</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -783,34 +771,34 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>RT_ms</t>
+          <t>Response</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Reaction time for the response, measured in milliseconds</t>
+          <t>Participant's response in the trial</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>48;47;0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Numerical</t>
+          <t>Categorical</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RT_sec</t>
+          <t>RT_ms</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Reaction time for the response, measured in seconds</t>
+          <t>Reaction time for the response, measured in milliseconds</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -827,20 +815,42 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>RT_sec</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Reaction time for the response, measured in seconds</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Numerical</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>ACC</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Accuracy of the participant's response</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>1;0</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Categorical</t>
         </is>
